--- a/Screen_5_Comparator_And_Outcomes/validation_data/stage_5_validation_workbook_50.xlsx
+++ b/Screen_5_Comparator_And_Outcomes/validation_data/stage_5_validation_workbook_50.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nhs-my.sharepoint.com/personal/akkshata_ahire_nhs_net/Documents/Documents/NHS - GitHub/NHSCRB/Screen_5_Comparator_And_Outcomes/validation_data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NM2.TP5IJ4AX\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="65" documentId="8_{193B0AB5-D142-4433-B571-1B09E36D9344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0AAC1DA1-ED98-4B9E-9DDB-182A2CEF9C2B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1930113E-14E3-4AC3-AECA-6CDDBE34B1D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-18820" yWindow="60" windowWidth="19430" windowHeight="10310" xr2:uid="{66513E08-89B8-4D61-A86D-819C01466699}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{66513E08-89B8-4D61-A86D-819C01466699}"/>
   </bookViews>
   <sheets>
     <sheet name="Stage_5_API_50" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="919" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="268">
   <si>
     <t>id</t>
   </si>
@@ -973,17 +973,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="6">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1041,36 +1031,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1405,9 +1365,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CCB2A6B-30B7-4231-94C6-6E4D3269210D}">
   <dimension ref="A1:K42"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1442,7 +1402,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1477,7 +1437,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1512,7 +1472,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1547,7 +1507,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -1582,7 +1542,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -1617,7 +1577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -1652,7 +1612,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -1687,7 +1647,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -1722,7 +1682,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -1757,7 +1717,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>31</v>
       </c>
@@ -1792,7 +1752,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -1827,7 +1787,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>42</v>
       </c>
@@ -1862,7 +1822,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>45</v>
       </c>
@@ -1897,7 +1857,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>47</v>
       </c>
@@ -1932,7 +1892,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>49</v>
       </c>
@@ -1967,7 +1927,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>50</v>
       </c>
@@ -2002,7 +1962,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>57</v>
       </c>
@@ -2037,7 +1997,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>60</v>
       </c>
@@ -2072,7 +2032,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>62</v>
       </c>
@@ -2107,7 +2067,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>71</v>
       </c>
@@ -2142,7 +2102,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>74</v>
       </c>
@@ -2177,7 +2137,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>76</v>
       </c>
@@ -2212,7 +2172,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>78</v>
       </c>
@@ -2247,7 +2207,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>83</v>
       </c>
@@ -2282,7 +2242,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>85</v>
       </c>
@@ -2317,7 +2277,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>91</v>
       </c>
@@ -2352,7 +2312,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>94</v>
       </c>
@@ -2387,7 +2347,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>99</v>
       </c>
@@ -2422,7 +2382,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>103</v>
       </c>
@@ -2457,7 +2417,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>106</v>
       </c>
@@ -2492,12 +2452,12 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="33" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="34" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="35" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="36" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="37" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="42" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="33" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="34" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="35" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="36" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="37" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="42" customFormat="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2506,159 +2466,159 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61D56000-B170-40EA-8241-FE1490451DA5}">
   <dimension ref="A1:A31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>106</v>
       </c>
@@ -2672,14 +2632,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D3E4052-2545-45A0-857B-B79114EE9774}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:H52"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="10.85546875" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" customWidth="1"/>
-    <col min="4" max="4" width="13.28515625" customWidth="1"/>
+    <col min="2" max="2" width="10.81640625" customWidth="1"/>
+    <col min="3" max="3" width="13.54296875" customWidth="1"/>
+    <col min="4" max="4" width="13.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>108</v>
       </c>
@@ -2705,7 +2665,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -2733,7 +2693,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -2761,7 +2721,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -2789,7 +2749,7 @@
         <v>J502</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -2817,7 +2777,7 @@
         <v>J503</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -2845,7 +2805,7 @@
         <v>J504</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -2873,7 +2833,7 @@
         <v>J505</v>
       </c>
     </row>
-    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -2901,7 +2861,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -2929,7 +2889,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -2957,7 +2917,7 @@
         <v>J508</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -2985,7 +2945,7 @@
         <v>J509</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -3013,7 +2973,7 @@
         <v>J510</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -3041,7 +3001,7 @@
         <v>J511</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -3065,7 +3025,7 @@
         <v>J512</v>
       </c>
     </row>
-    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -3093,7 +3053,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -3121,7 +3081,7 @@
         <v>J514</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -3149,7 +3109,7 @@
         <v>J515</v>
       </c>
     </row>
-    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -3177,7 +3137,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="19" spans="1:8" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>36</v>
       </c>
@@ -3205,7 +3165,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>38</v>
       </c>
@@ -3233,7 +3193,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>40</v>
       </c>
@@ -3261,7 +3221,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>42</v>
       </c>
@@ -3289,7 +3249,7 @@
         <v>J520</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>45</v>
       </c>
@@ -3317,7 +3277,7 @@
         <v>J521</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>47</v>
       </c>
@@ -3345,7 +3305,7 @@
         <v>J522</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>49</v>
       </c>
@@ -3373,7 +3333,7 @@
         <v>J523</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>50</v>
       </c>
@@ -3401,7 +3361,7 @@
         <v>J524</v>
       </c>
     </row>
-    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>51</v>
       </c>
@@ -3429,7 +3389,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>54</v>
       </c>
@@ -3457,7 +3417,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>57</v>
       </c>
@@ -3485,7 +3445,7 @@
         <v>J527</v>
       </c>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>59</v>
       </c>
@@ -3513,7 +3473,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>60</v>
       </c>
@@ -3541,7 +3501,7 @@
         <v>J529</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>62</v>
       </c>
@@ -3569,7 +3529,7 @@
         <v>J530</v>
       </c>
     </row>
-    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>64</v>
       </c>
@@ -3597,7 +3557,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>66</v>
       </c>
@@ -3625,7 +3585,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>69</v>
       </c>
@@ -3653,7 +3613,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>71</v>
       </c>
@@ -3681,7 +3641,7 @@
         <v>J534</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>74</v>
       </c>
@@ -3709,7 +3669,7 @@
         <v>J535</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>76</v>
       </c>
@@ -3737,7 +3697,7 @@
         <v>J536</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>78</v>
       </c>
@@ -3762,7 +3722,7 @@
         <v>J537</v>
       </c>
     </row>
-    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>80</v>
       </c>
@@ -3790,7 +3750,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>82</v>
       </c>
@@ -3818,7 +3778,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>83</v>
       </c>
@@ -3846,7 +3806,7 @@
         <v>J540</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>85</v>
       </c>
@@ -3874,7 +3834,7 @@
         <v>J541</v>
       </c>
     </row>
-    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>88</v>
       </c>
@@ -3902,7 +3862,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>89</v>
       </c>
@@ -3930,7 +3890,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>91</v>
       </c>
@@ -3958,7 +3918,7 @@
         <v>J544</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>94</v>
       </c>
@@ -3986,7 +3946,7 @@
         <v>J545</v>
       </c>
     </row>
-    <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>97</v>
       </c>
@@ -4014,7 +3974,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>99</v>
       </c>
@@ -4042,7 +4002,7 @@
         <v>J547</v>
       </c>
     </row>
-    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>102</v>
       </c>
@@ -4070,7 +4030,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>103</v>
       </c>
@@ -4098,7 +4058,7 @@
         <v>J549</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>106</v>
       </c>
@@ -4164,13 +4124,11 @@
     </filterColumn>
   </autoFilter>
   <conditionalFormatting sqref="E1:E52 F50:F52">
-    <cfRule type="containsText" dxfId="7" priority="2" operator="containsText" text="Include">
+    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="Exclude">
+      <formula>NOT(ISERROR(SEARCH("Exclude",E1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="Include">
       <formula>NOT(ISERROR(SEARCH("Include",E1)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E1:E52 F50:F52">
-    <cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="Exclude">
-      <formula>NOT(ISERROR(SEARCH("Exclude",E1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4180,11 +4138,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1235A4A9-643F-403F-8F39-91437DA8F632}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:O31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4231,7 +4188,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="2" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -4278,7 +4235,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -4325,7 +4282,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -4372,7 +4329,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -4419,7 +4376,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -4466,7 +4423,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -4513,7 +4470,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -4560,7 +4517,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -4607,7 +4564,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -4654,7 +4611,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>31</v>
       </c>
@@ -4701,7 +4658,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -4748,7 +4705,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>42</v>
       </c>
@@ -4795,7 +4752,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>45</v>
       </c>
@@ -4842,7 +4799,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>47</v>
       </c>
@@ -4889,7 +4846,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>49</v>
       </c>
@@ -4936,7 +4893,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>50</v>
       </c>
@@ -4983,7 +4940,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>57</v>
       </c>
@@ -5030,7 +4987,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="19" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>60</v>
       </c>
@@ -5077,7 +5034,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>62</v>
       </c>
@@ -5124,7 +5081,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>71</v>
       </c>
@@ -5171,7 +5128,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>74</v>
       </c>
@@ -5218,7 +5175,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="23" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>76</v>
       </c>
@@ -5265,7 +5222,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>78</v>
       </c>
@@ -5306,13 +5263,13 @@
         <v>257</v>
       </c>
       <c r="N24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O24" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>83</v>
       </c>
@@ -5359,7 +5316,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>85</v>
       </c>
@@ -5406,7 +5363,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="27" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>91</v>
       </c>
@@ -5453,7 +5410,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="28" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>94</v>
       </c>
@@ -5500,7 +5457,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="29" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>99</v>
       </c>
@@ -5547,7 +5504,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="30" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>103</v>
       </c>
@@ -5594,7 +5551,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="31" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>106</v>
       </c>
@@ -5642,26 +5599,12 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O31" xr:uid="{1235A4A9-643F-403F-8F39-91437DA8F632}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="TRUE"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="13">
-      <filters>
-        <filter val="FALSE"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
-  <conditionalFormatting sqref="M30:M31 L1:L31">
-    <cfRule type="containsText" dxfId="5" priority="2" operator="containsText" text="Include">
+  <conditionalFormatting sqref="L1:L31 M30:M31">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="Exclude">
+      <formula>NOT(ISERROR(SEARCH("Exclude",L1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="Include">
       <formula>NOT(ISERROR(SEARCH("Include",L1)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M30:M31 L1:L31">
-    <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="Exclude">
-      <formula>NOT(ISERROR(SEARCH("Exclude",L1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5670,18 +5613,18 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60927BCB-4710-4D9A-A38E-921B487297AE}">
-  <dimension ref="A1:O33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:O32"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>163</v>
       </c>
@@ -5689,20 +5632,20 @@
         <v>164</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>161</v>
       </c>
       <c r="B3">
         <f>COUNTIFS('Merged results table'!$E:$E,TRUE,'Merged results table'!$N:$N,TRUE)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3">
         <f>COUNTIFS('Merged results table'!$E:$E,TRUE,'Merged results table'!$N:$N,FALSE)</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>162</v>
       </c>
@@ -5715,16 +5658,16 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>168</v>
       </c>
       <c r="B6">
         <f>B3</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>169</v>
       </c>
@@ -5733,16 +5676,16 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>170</v>
       </c>
       <c r="B8">
         <f>C3</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>171</v>
       </c>
@@ -5751,35 +5694,35 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>166</v>
       </c>
       <c r="B11">
         <f>(B3+C4)/(B3+B4+C3+C4)</f>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.6333333333333333</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>167</v>
       </c>
       <c r="B12">
         <f>B3/(B3+B4)</f>
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0.76923076923076927</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>0</v>
       </c>
@@ -5826,7 +5769,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>32</v>
       </c>
@@ -5873,7 +5816,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>76</v>
       </c>
@@ -5920,7 +5863,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>103</v>
       </c>
@@ -5967,12 +5910,12 @@
         <v>103</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
         <v>0</v>
       </c>
@@ -6019,7 +5962,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>10</v>
       </c>
@@ -6066,7 +6009,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>14</v>
       </c>
@@ -6113,7 +6056,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>49</v>
       </c>
@@ -6160,7 +6103,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>50</v>
       </c>
@@ -6207,7 +6150,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>57</v>
       </c>
@@ -6254,7 +6197,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>62</v>
       </c>
@@ -6301,7 +6244,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>74</v>
       </c>
@@ -6348,24 +6291,24 @@
         <v>74</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B32">
         <v>2019</v>
       </c>
       <c r="C32" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D32" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="E32" t="b">
         <v>1</v>
       </c>
       <c r="F32" t="s">
-        <v>215</v>
+        <v>244</v>
       </c>
       <c r="G32" t="b">
         <v>1</v>
@@ -6377,90 +6320,31 @@
         <v>1</v>
       </c>
       <c r="J32" t="s">
-        <v>211</v>
+        <v>245</v>
       </c>
       <c r="K32">
         <v>0.9</v>
       </c>
       <c r="L32" t="s">
-        <v>112</v>
+        <v>173</v>
       </c>
       <c r="M32" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="N32" t="b">
         <v>0</v>
       </c>
       <c r="O32" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
         <v>83</v>
       </c>
-      <c r="B33">
-        <v>2019</v>
-      </c>
-      <c r="C33" t="s">
-        <v>84</v>
-      </c>
-      <c r="D33" t="s">
-        <v>200</v>
-      </c>
-      <c r="E33" t="b">
-        <v>1</v>
-      </c>
-      <c r="F33" t="s">
-        <v>244</v>
-      </c>
-      <c r="G33" t="b">
-        <v>1</v>
-      </c>
-      <c r="H33" t="s">
-        <v>216</v>
-      </c>
-      <c r="I33" t="b">
-        <v>1</v>
-      </c>
-      <c r="J33" t="s">
-        <v>245</v>
-      </c>
-      <c r="K33">
-        <v>0.9</v>
-      </c>
-      <c r="L33" t="s">
-        <v>173</v>
-      </c>
-      <c r="M33" t="s">
-        <v>256</v>
-      </c>
-      <c r="N33" t="b">
-        <v>0</v>
-      </c>
-      <c r="O33" t="s">
-        <v>83</v>
-      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="M20 L17:L20">
-    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="Include">
-      <formula>NOT(ISERROR(SEARCH("Include",L17)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M20 L17:L20">
-    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="Exclude">
+  <conditionalFormatting sqref="L17:L20 M20 L24:L32">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="Exclude">
       <formula>NOT(ISERROR(SEARCH("Exclude",L17)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L24:L33">
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Include">
-      <formula>NOT(ISERROR(SEARCH("Include",L24)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L24:L33">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Exclude">
-      <formula>NOT(ISERROR(SEARCH("Exclude",L24)))</formula>
+    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="Include">
+      <formula>NOT(ISERROR(SEARCH("Include",L17)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
